--- a/stage-6/64_launch_scorecard.xlsx
+++ b/stage-6/64_launch_scorecard.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch checklist" sheetId="1" r:id="R2616ee8970c648c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilot metrics" sheetId="2" r:id="Rd8b6ef9a813f4710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review log" sheetId="3" r:id="Rc1a63ed0a7fb45e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision gate" sheetId="4" r:id="R570d98f1c39f4d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch checklist" sheetId="1" r:id="Reacfc4b4912e4211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilot metrics" sheetId="2" r:id="R88e092cbe19a4058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review log" sheetId="3" r:id="Rd10ac53d67c042be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision gate" sheetId="4" r:id="Re19805c88cf44b05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -844,34 +844,34 @@
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="40" t="str">
-        <x:v>Repeat contacts per case</x:v>
+        <x:v>Confirmed resolution within promised SLA</x:v>
       </x:c>
       <x:c r="B5" s="40" t="str">
         <x:v>Primary</x:v>
       </x:c>
       <x:c r="C5" s="40" t="str">
-        <x:v>Lower</x:v>
+        <x:v>Higher</x:v>
       </x:c>
       <x:c r="D5" s="45"/>
       <x:c r="E5" s="45"/>
       <x:c r="F5" s="45"/>
       <x:c r="G5" s="46" t="str">
-        <x:f>IF(OR(D5="",E5="",F5=""),"Awaiting real data",IF(E5&lt;F5,"Review","Pass"))</x:f>
+        <x:f>IF(OR(E5="",F5=""),"Awaiting real data",IF(E5&gt;=F5,"Pass","Review"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H5" s="40" t="str">
-        <x:v>Support Ops</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="I5" s="40" t="str">
-        <x:v>Compare with approved baseline</x:v>
+        <x:v>Pre-register target before pilot</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="41" t="str">
-        <x:v>Confirmed-resolution time (hours)</x:v>
+        <x:v>Repeat contacts per case</x:v>
       </x:c>
       <x:c r="B6" s="41" t="str">
-        <x:v>Primary</x:v>
+        <x:v>Secondary</x:v>
       </x:c>
       <x:c r="C6" s="41" t="str">
         <x:v>Lower</x:v>
@@ -880,11 +880,11 @@
       <x:c r="E6" s="47"/>
       <x:c r="F6" s="47"/>
       <x:c r="G6" s="48" t="str">
-        <x:f>IF(OR(D6="",E6="",F6=""),"Awaiting real data",IF(E6&lt;F6,"Review","Pass"))</x:f>
+        <x:f>IF(OR(D6="",E6="",F6=""),"Awaiting real data",IF(E6&lt;=F6,"Pass","Review"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H6" s="41" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Support Ops</x:v>
       </x:c>
       <x:c r="I6" s="41" t="str">
         <x:v>Compare with approved baseline</x:v>
@@ -892,33 +892,31 @@
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="41" t="str">
-        <x:v>Understood-next rate</x:v>
+        <x:v>Confirmed-resolution time (hours)</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>Customer</x:v>
+        <x:v>Secondary</x:v>
       </x:c>
       <x:c r="C7" s="41" t="str">
-        <x:v>Higher</x:v>
+        <x:v>Lower</x:v>
       </x:c>
       <x:c r="D7" s="47"/>
       <x:c r="E7" s="47"/>
-      <x:c r="F7" s="47" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="F7" s="47"/>
       <x:c r="G7" s="48" t="str">
-        <x:f>IF(E7="","Awaiting real data",IF(E7&gt;=F7,"Pass","Fail"))</x:f>
+        <x:f>IF(OR(D7="",E7="",F7=""),"Awaiting real data",IF(E7&lt;=F7,"Pass","Review"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H7" s="41" t="str">
-        <x:v>UX Research</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="I7" s="41" t="str">
-        <x:v>Sampled-case or research evidence</x:v>
+        <x:v>Compare with approved baseline</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="41" t="str">
-        <x:v>Recovery completion rate</x:v>
+        <x:v>Understood-next rate</x:v>
       </x:c>
       <x:c r="B8" s="41" t="str">
         <x:v>Customer</x:v>
@@ -928,47 +926,47 @@
       </x:c>
       <x:c r="D8" s="47"/>
       <x:c r="E8" s="47"/>
-      <x:c r="F8" s="47"/>
+      <x:c r="F8" s="47" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
       <x:c r="G8" s="48" t="str">
-        <x:f>IF(OR(D8="",E8="",F8=""),"Awaiting real data",IF(E8&gt;=F8,"Pass","Review"))</x:f>
+        <x:f>IF(E8="","Awaiting real data",IF(E8&gt;=F8,"Pass","Fail"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H8" s="41" t="str">
-        <x:v>Product</x:v>
+        <x:v>UX Research</x:v>
       </x:c>
       <x:c r="I8" s="41" t="str">
-        <x:v>Compare with approved baseline</x:v>
+        <x:v>Sampled-case or research evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="41" t="str">
-        <x:v>Incorrect recovery rate</x:v>
+        <x:v>Recovery completion rate</x:v>
       </x:c>
       <x:c r="B9" s="41" t="str">
-        <x:v>Guardrail</x:v>
+        <x:v>Secondary customer</x:v>
       </x:c>
       <x:c r="C9" s="41" t="str">
-        <x:v>Zero</x:v>
+        <x:v>Higher</x:v>
       </x:c>
       <x:c r="D9" s="47"/>
       <x:c r="E9" s="47"/>
-      <x:c r="F9" s="47" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="F9" s="47"/>
       <x:c r="G9" s="48" t="str">
-        <x:f>IF(E9="","Awaiting real data",IF(E9&lt;=F9,"Pass","Fail"))</x:f>
+        <x:f>IF(OR(D9="",E9="",F9=""),"Awaiting real data",IF(E9&gt;=F9,"Pass","Review"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H9" s="41" t="str">
-        <x:v>Policy / Payments</x:v>
+        <x:v>Product</x:v>
       </x:c>
       <x:c r="I9" s="41" t="str">
-        <x:v>Zero tolerated</x:v>
+        <x:v>Compare with approved baseline</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="41" t="str">
-        <x:v>False final outcome</x:v>
+        <x:v>Incorrect recovery rate</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
         <x:v>Guardrail</x:v>
@@ -986,7 +984,7 @@
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H10" s="41" t="str">
-        <x:v>Product / Engineering</x:v>
+        <x:v>Policy / Payments</x:v>
       </x:c>
       <x:c r="I10" s="41" t="str">
         <x:v>Zero tolerated</x:v>
@@ -994,7 +992,7 @@
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="41" t="str">
-        <x:v>Duplicate financial action</x:v>
+        <x:v>False final outcome</x:v>
       </x:c>
       <x:c r="B11" s="41" t="str">
         <x:v>Guardrail</x:v>
@@ -1012,7 +1010,7 @@
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H11" s="41" t="str">
-        <x:v>Payments</x:v>
+        <x:v>Product / Engineering</x:v>
       </x:c>
       <x:c r="I11" s="41" t="str">
         <x:v>Zero tolerated</x:v>
@@ -1020,36 +1018,36 @@
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="41" t="str">
-        <x:v>Event conflict rate</x:v>
+        <x:v>Duplicate financial action</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
-        <x:v>Data quality</x:v>
+        <x:v>Guardrail</x:v>
       </x:c>
       <x:c r="C12" s="41" t="str">
-        <x:v>Lower</x:v>
+        <x:v>Zero</x:v>
       </x:c>
       <x:c r="D12" s="47"/>
       <x:c r="E12" s="47"/>
       <x:c r="F12" s="47" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="48" t="str">
-        <x:f>IF(E12="","Awaiting real data",IF(E12&lt;=F12,"Pass","Review"))</x:f>
+        <x:f>IF(E12="","Awaiting real data",IF(E12&lt;=F12,"Pass","Fail"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H12" s="41" t="str">
-        <x:v>Engineering</x:v>
+        <x:v>Payments</x:v>
       </x:c>
       <x:c r="I12" s="41" t="str">
-        <x:v>Pilot ceiling</x:v>
+        <x:v>Zero tolerated</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="41" t="str">
-        <x:v>SLA breach rate</x:v>
+        <x:v>Event conflict rate</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Data quality</x:v>
       </x:c>
       <x:c r="C13" s="41" t="str">
         <x:v>Lower</x:v>
@@ -1057,14 +1055,14 @@
       <x:c r="D13" s="47"/>
       <x:c r="E13" s="47"/>
       <x:c r="F13" s="47" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="G13" s="48" t="str">
         <x:f>IF(E13="","Awaiting real data",IF(E13&lt;=F13,"Pass","Review"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H13" s="41" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Engineering</x:v>
       </x:c>
       <x:c r="I13" s="41" t="str">
         <x:v>Pilot ceiling</x:v>
@@ -1072,7 +1070,7 @@
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="41" t="str">
-        <x:v>Support handle-time increase</x:v>
+        <x:v>SLA breach rate</x:v>
       </x:c>
       <x:c r="B14" s="41" t="str">
         <x:v>Operations</x:v>
@@ -1083,55 +1081,70 @@
       <x:c r="D14" s="47"/>
       <x:c r="E14" s="47"/>
       <x:c r="F14" s="47" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="G14" s="48" t="str">
         <x:f>IF(E14="","Awaiting real data",IF(E14&lt;=F14,"Pass","Review"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
       <x:c r="H14" s="41" t="str">
-        <x:v>Support Ops</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="I14" s="41" t="str">
-        <x:v>Maximum increase versus baseline</x:v>
+        <x:v>Pilot ceiling</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="41" t="str">
-        <x:v>Case-linkage completeness</x:v>
+        <x:v>Support handle-time increase</x:v>
       </x:c>
       <x:c r="B15" s="41" t="str">
-        <x:v>Data quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="C15" s="41" t="str">
-        <x:v>Higher</x:v>
+        <x:v>Lower</x:v>
       </x:c>
       <x:c r="D15" s="47"/>
       <x:c r="E15" s="47"/>
       <x:c r="F15" s="47" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="G15" s="48" t="str">
+        <x:f>IF(E15="","Awaiting real data",IF(E15&lt;=F15,"Pass","Review"))</x:f>
+        <x:v>Awaiting real data</x:v>
+      </x:c>
+      <x:c r="H15" s="41" t="str">
+        <x:v>Support Ops</x:v>
+      </x:c>
+      <x:c r="I15" s="41" t="str">
+        <x:v>Maximum increase versus baseline</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="41" t="str">
+        <x:v>Case-linkage completeness</x:v>
+      </x:c>
+      <x:c r="B16" s="41" t="str">
+        <x:v>Data quality</x:v>
+      </x:c>
+      <x:c r="C16" s="41" t="str">
+        <x:v>Higher</x:v>
+      </x:c>
+      <x:c r="D16" s="47"/>
+      <x:c r="E16" s="47"/>
+      <x:c r="F16" s="47" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="G15" s="48" t="str">
-        <x:f>IF(E15="","Awaiting real data",IF(E15&gt;=F15,"Pass","Fail"))</x:f>
+      <x:c r="G16" s="48" t="str">
+        <x:f>IF(E16="","Awaiting real data",IF(E16&gt;=F16,"Pass","Fail"))</x:f>
         <x:v>Awaiting real data</x:v>
       </x:c>
-      <x:c r="H15" s="41" t="str">
+      <x:c r="H16" s="41" t="str">
         <x:v>Analytics</x:v>
       </x:c>
-      <x:c r="I15" s="41" t="str">
+      <x:c r="I16" s="41" t="str">
         <x:v>No decision below 95%</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="35"/>
-      <x:c r="B16" s="35"/>
-      <x:c r="C16" s="35"/>
-      <x:c r="D16" s="35"/>
-      <x:c r="E16" s="35"/>
-      <x:c r="F16" s="35"/>
-      <x:c r="G16" s="35"/>
-      <x:c r="H16" s="35"/>
-      <x:c r="I16" s="35"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="44" t="str">
@@ -1434,10 +1447,10 @@
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="41" t="str">
-        <x:v>Primary outcomes pass</x:v>
+        <x:v>Primary outcome passes</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>Repeat contact and resolution outcomes meet target</x:v>
+        <x:v>Confirmed resolution within promised SLA meets the approved target</x:v>
       </x:c>
       <x:c r="C7" s="41" t="str">
         <x:v>Pending</x:v>
@@ -1446,7 +1459,9 @@
       <x:c r="E7" s="41" t="str">
         <x:v>Product</x:v>
       </x:c>
-      <x:c r="F7" s="41" t="str"/>
+      <x:c r="F7" s="41" t="str">
+        <x:v>Repeat contacts and comprehension must not regress</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="41" t="str">
